--- a/database/controller_excel/Resguardo_Alejandro_Cancino_Argüello.xlsx
+++ b/database/controller_excel/Resguardo_Alejandro_Cancino_Argüello.xlsx
@@ -41,13 +41,13 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>20/01/2026</t>
+    <t>21/01/2026</t>
   </si>
   <si>
     <t>Área:</t>
   </si>
   <si>
-    <t>qwert56</t>
+    <t>&lt;wazse</t>
   </si>
   <si>
     <t>Región:</t>
@@ -59,7 +59,7 @@
     <t>Ubicación:</t>
   </si>
   <si>
-    <t>zt</t>
+    <t>sezdrx</t>
   </si>
   <si>
     <t>Por medio de la presente hago constar que la empresa: DIAVAZ me otorga las siguientes herramientas de trabajo para desempeñar mis funciones:</t>
